--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/154.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/154.xlsx
@@ -426,13 +426,13 @@
         <v>-1.087692000638735</v>
       </c>
       <c r="E2">
-        <v>-15.53947421945046</v>
+        <v>-17.77563468443808</v>
       </c>
       <c r="F2">
-        <v>-2.11645980894998</v>
+        <v>-3.068094079857872</v>
       </c>
       <c r="G2">
-        <v>-7.600252283360947</v>
+        <v>-8.86638366703737</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-1.835981744795552</v>
       </c>
       <c r="E3">
-        <v>-16.25226508520579</v>
+        <v>-17.43770184008969</v>
       </c>
       <c r="F3">
-        <v>-2.512073169913774</v>
+        <v>-3.008991722402933</v>
       </c>
       <c r="G3">
-        <v>-6.882075776253613</v>
+        <v>-8.493063378210376</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.764010363775119</v>
       </c>
       <c r="E4">
-        <v>-15.14332331325945</v>
+        <v>-17.31930941563315</v>
       </c>
       <c r="F4">
-        <v>-2.59932345171584</v>
+        <v>-2.733911617118287</v>
       </c>
       <c r="G4">
-        <v>-7.309702254106811</v>
+        <v>-8.541586044179473</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.755358006335378</v>
       </c>
       <c r="E5">
-        <v>-17.49410851232923</v>
+        <v>-19.12445425304472</v>
       </c>
       <c r="F5">
-        <v>-2.496447675594767</v>
+        <v>-2.677721799451591</v>
       </c>
       <c r="G5">
-        <v>-6.936391896916435</v>
+        <v>-7.957983213243513</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.787830651182501</v>
       </c>
       <c r="E6">
-        <v>-17.60159637137529</v>
+        <v>-19.92075923644951</v>
       </c>
       <c r="F6">
-        <v>-3.129730413197975</v>
+        <v>-2.576848187343084</v>
       </c>
       <c r="G6">
-        <v>-7.282923251239646</v>
+        <v>-8.054048623702084</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.793006665750556</v>
       </c>
       <c r="E7">
-        <v>-17.55637050146069</v>
+        <v>-20.90239654709221</v>
       </c>
       <c r="F7">
-        <v>-2.654170485822598</v>
+        <v>-2.542588568298102</v>
       </c>
       <c r="G7">
-        <v>-6.928655151991158</v>
+        <v>-9.675040694278525</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.724526546421755</v>
       </c>
       <c r="E8">
-        <v>-19.77030521601866</v>
+        <v>-21.49933546230931</v>
       </c>
       <c r="F8">
-        <v>-2.889793794977098</v>
+        <v>-2.512517174841674</v>
       </c>
       <c r="G8">
-        <v>-6.63911814967204</v>
+        <v>-8.399818552551263</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.527751952115827</v>
       </c>
       <c r="E9">
-        <v>-20.54508636246499</v>
+        <v>-22.40682353955042</v>
       </c>
       <c r="F9">
-        <v>-2.531660745520371</v>
+        <v>-2.592824909440878</v>
       </c>
       <c r="G9">
-        <v>-5.866145492798688</v>
+        <v>-8.800414426076312</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.156246261833507</v>
       </c>
       <c r="E10">
-        <v>-21.5406623161033</v>
+        <v>-23.08611728307101</v>
       </c>
       <c r="F10">
-        <v>-2.432636877822315</v>
+        <v>-2.117945900070603</v>
       </c>
       <c r="G10">
-        <v>-6.70084989234283</v>
+        <v>-8.981196696884833</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.570131302459245</v>
       </c>
       <c r="E11">
-        <v>-23.34698002828286</v>
+        <v>-23.97289664867504</v>
       </c>
       <c r="F11">
-        <v>-2.230875571359454</v>
+        <v>-2.034028140329998</v>
       </c>
       <c r="G11">
-        <v>-5.981008180829241</v>
+        <v>-8.877536894959174</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.742814331720057</v>
       </c>
       <c r="E12">
-        <v>-23.377764594587</v>
+        <v>-24.07219249824123</v>
       </c>
       <c r="F12">
-        <v>-2.120961157416793</v>
+        <v>-2.028632155068163</v>
       </c>
       <c r="G12">
-        <v>-6.060368578496651</v>
+        <v>-7.636618626109841</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.656983680273779</v>
       </c>
       <c r="E13">
-        <v>-23.46097530447794</v>
+        <v>-25.99444820196516</v>
       </c>
       <c r="F13">
-        <v>-1.792184620347877</v>
+        <v>-1.957505216394186</v>
       </c>
       <c r="G13">
-        <v>-5.162684360613415</v>
+        <v>-7.746482390376094</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.311566946978509</v>
       </c>
       <c r="E14">
-        <v>-24.12370389007848</v>
+        <v>-26.32501774757708</v>
       </c>
       <c r="F14">
-        <v>-1.696680485744317</v>
+        <v>-1.863975909678899</v>
       </c>
       <c r="G14">
-        <v>-4.297612326837539</v>
+        <v>-7.11883606158567</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.715021938814987</v>
       </c>
       <c r="E15">
-        <v>-25.72441076841377</v>
+        <v>-26.94840295099897</v>
       </c>
       <c r="F15">
-        <v>-1.473762675813956</v>
+        <v>-1.845717863753795</v>
       </c>
       <c r="G15">
-        <v>-5.578445843253865</v>
+        <v>-6.12987017154811</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.890024261012404</v>
       </c>
       <c r="E16">
-        <v>-27.56631322934559</v>
+        <v>-27.86279242262777</v>
       </c>
       <c r="F16">
-        <v>-1.575337915112634</v>
+        <v>-1.555024689661185</v>
       </c>
       <c r="G16">
-        <v>-3.929784233060197</v>
+        <v>-5.577297083951739</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.870052848804789</v>
       </c>
       <c r="E17">
-        <v>-27.13117669042255</v>
+        <v>-29.38298303310668</v>
       </c>
       <c r="F17">
-        <v>-0.7784062268819668</v>
+        <v>-1.116386754163387</v>
       </c>
       <c r="G17">
-        <v>-2.740838218631882</v>
+        <v>-5.553510814252075</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.692940286011728</v>
       </c>
       <c r="E18">
-        <v>-28.65814642649094</v>
+        <v>-30.28602641310926</v>
       </c>
       <c r="F18">
-        <v>-1.274580077076009</v>
+        <v>-1.589506311170117</v>
       </c>
       <c r="G18">
-        <v>-1.961688083782251</v>
+        <v>-5.142536380461411</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.408721947131164</v>
       </c>
       <c r="E19">
-        <v>-28.86477163851293</v>
+        <v>-30.76553973307046</v>
       </c>
       <c r="F19">
-        <v>-1.108719385483075</v>
+        <v>-1.153837244443953</v>
       </c>
       <c r="G19">
-        <v>-3.130300727508362</v>
+        <v>-5.110659137463768</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-2.069109823560645</v>
       </c>
       <c r="E20">
-        <v>-30.02747998235233</v>
+        <v>-31.71404219939904</v>
       </c>
       <c r="F20">
-        <v>-1.000759918611021</v>
+        <v>-0.7655524498927269</v>
       </c>
       <c r="G20">
-        <v>-1.824300443902496</v>
+        <v>-4.261947819742971</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.722401429902581</v>
       </c>
       <c r="E21">
-        <v>-31.04284310316716</v>
+        <v>-31.91804995344459</v>
       </c>
       <c r="F21">
-        <v>-0.8717872558321522</v>
+        <v>-0.7423830136364247</v>
       </c>
       <c r="G21">
-        <v>-1.939312106482317</v>
+        <v>-4.425263652286297</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.5767797734228425</v>
       </c>
       <c r="E22">
-        <v>-28.76705169790141</v>
+        <v>-34.43290403004927</v>
       </c>
       <c r="F22">
-        <v>-0.5750105515333818</v>
+        <v>-0.4413244782325836</v>
       </c>
       <c r="G22">
-        <v>-1.706464885977678</v>
+        <v>-3.282155451394731</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.780271990491585</v>
       </c>
       <c r="E23">
-        <v>-30.96378273970425</v>
+        <v>-33.54644392186277</v>
       </c>
       <c r="F23">
-        <v>-0.9265150050329072</v>
+        <v>-0.1393141486829258</v>
       </c>
       <c r="G23">
-        <v>-0.004986832250476321</v>
+        <v>-3.87276008614625</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>2.850403316724427</v>
       </c>
       <c r="E24">
-        <v>-32.36936899423404</v>
+        <v>-35.53282281753531</v>
       </c>
       <c r="F24">
-        <v>-0.6323054113154124</v>
+        <v>-0.3090134948204325</v>
       </c>
       <c r="G24">
-        <v>-0.5032735940938791</v>
+        <v>-3.247119947952624</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.750084131610098</v>
       </c>
       <c r="E25">
-        <v>-32.9635681826765</v>
+        <v>-34.37025485639015</v>
       </c>
       <c r="F25">
-        <v>-0.371518785566072</v>
+        <v>-0.1209011980534984</v>
       </c>
       <c r="G25">
-        <v>-2.067956595592856</v>
+        <v>-3.927062964626916</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>4.455385515887673</v>
       </c>
       <c r="E26">
-        <v>-31.92312184433318</v>
+        <v>-34.58887373182145</v>
       </c>
       <c r="F26">
-        <v>0.3536448076208516</v>
+        <v>0.06283649045925155</v>
       </c>
       <c r="G26">
-        <v>-1.757712130925596</v>
+        <v>-3.798007967869507</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>4.955987943843481</v>
       </c>
       <c r="E27">
-        <v>-32.70864453112571</v>
+        <v>-34.52351426646874</v>
       </c>
       <c r="F27">
-        <v>-0.01621378242250248</v>
+        <v>-0.4269829533879157</v>
       </c>
       <c r="G27">
-        <v>-1.729863821849247</v>
+        <v>-2.969547257212432</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>5.244997032422368</v>
       </c>
       <c r="E28">
-        <v>-33.80988336878499</v>
+        <v>-34.92538689956844</v>
       </c>
       <c r="F28">
-        <v>0.1691972082439025</v>
+        <v>-0.5439210945389136</v>
       </c>
       <c r="G28">
-        <v>-0.8540325150707399</v>
+        <v>-3.335551240397636</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>5.329444370188992</v>
       </c>
       <c r="E29">
-        <v>-33.78630360462705</v>
+        <v>-34.40989485361629</v>
       </c>
       <c r="F29">
-        <v>-0.2626613684293834</v>
+        <v>-0.5558404730977956</v>
       </c>
       <c r="G29">
-        <v>-1.031219533423612</v>
+        <v>-3.902889361099157</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>5.228481274846327</v>
       </c>
       <c r="E30">
-        <v>-32.47994527255333</v>
+        <v>-34.31906498620744</v>
       </c>
       <c r="F30">
-        <v>-0.1281262185407157</v>
+        <v>-0.08762070927862546</v>
       </c>
       <c r="G30">
-        <v>-1.464275305961215</v>
+        <v>-3.171493845653513</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>4.96427126053359</v>
       </c>
       <c r="E31">
-        <v>-33.18913826570957</v>
+        <v>-34.57542189978167</v>
       </c>
       <c r="F31">
-        <v>-0.06939745478443914</v>
+        <v>-0.1996698260183006</v>
       </c>
       <c r="G31">
-        <v>-3.195968708825345</v>
+        <v>-3.654485887105483</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>4.561349434541058</v>
       </c>
       <c r="E32">
-        <v>-31.77243460749095</v>
+        <v>-33.35886547151705</v>
       </c>
       <c r="F32">
-        <v>-0.6033092387478185</v>
+        <v>-0.4410138404565337</v>
       </c>
       <c r="G32">
-        <v>-0.3243518498784285</v>
+        <v>-3.891004502613174</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>4.043516544878005</v>
       </c>
       <c r="E33">
-        <v>-32.64979021868502</v>
+        <v>-33.73818856829556</v>
       </c>
       <c r="F33">
-        <v>-0.04143425636813623</v>
+        <v>-0.6424935020024435</v>
       </c>
       <c r="G33">
-        <v>-1.443021603599095</v>
+        <v>-3.221175202561356</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>3.431822372607573</v>
       </c>
       <c r="E34">
-        <v>-31.88807598398782</v>
+        <v>-32.73618218156635</v>
       </c>
       <c r="F34">
-        <v>-0.7222884771793143</v>
+        <v>-0.5743635965917954</v>
       </c>
       <c r="G34">
-        <v>-1.777926321988386</v>
+        <v>-3.567895257980306</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>2.740956458274161</v>
       </c>
       <c r="E35">
-        <v>-32.86170242411095</v>
+        <v>-32.91352854489174</v>
       </c>
       <c r="F35">
-        <v>-0.3258160992188177</v>
+        <v>-0.07021173994139104</v>
       </c>
       <c r="G35">
-        <v>-3.413590730394876</v>
+        <v>-3.842256719547406</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.984372429947824</v>
       </c>
       <c r="E36">
-        <v>-31.57300287643015</v>
+        <v>-33.13906919284376</v>
       </c>
       <c r="F36">
-        <v>-0.2443445084186807</v>
+        <v>-0.1041259297794056</v>
       </c>
       <c r="G36">
-        <v>-2.886846519095898</v>
+        <v>-4.658104251699858</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.177357512430931</v>
       </c>
       <c r="E37">
-        <v>-30.44064210115315</v>
+        <v>-32.36389859763277</v>
       </c>
       <c r="F37">
-        <v>-0.4694798578863359</v>
+        <v>-0.3721823078557144</v>
       </c>
       <c r="G37">
-        <v>-2.704531465702694</v>
+        <v>-4.81494134662283</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.3314468764875618</v>
       </c>
       <c r="E38">
-        <v>-31.0141167282995</v>
+        <v>-31.98481550997668</v>
       </c>
       <c r="F38">
-        <v>-0.552889000041621</v>
+        <v>-0.4729954491438171</v>
       </c>
       <c r="G38">
-        <v>-2.147138223801144</v>
+        <v>-4.75325595158959</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.5344401264603016</v>
       </c>
       <c r="E39">
-        <v>-31.2848651322701</v>
+        <v>-30.72164297027711</v>
       </c>
       <c r="F39">
-        <v>-0.1333813813440758</v>
+        <v>-0.2986133420782847</v>
       </c>
       <c r="G39">
-        <v>-3.223012555335651</v>
+        <v>-3.897850710788386</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.397310999825321</v>
       </c>
       <c r="E40">
-        <v>-30.21974313905899</v>
+        <v>-30.97000939146479</v>
       </c>
       <c r="F40">
-        <v>0.4157102352756045</v>
+        <v>-0.5393841262737806</v>
       </c>
       <c r="G40">
-        <v>-1.467271349674256</v>
+        <v>-5.072011828838316</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.240498882847922</v>
       </c>
       <c r="E41">
-        <v>-28.55844754273808</v>
+        <v>-30.24908538639169</v>
       </c>
       <c r="F41">
-        <v>-0.1760447876904587</v>
+        <v>-0.217702556009843</v>
       </c>
       <c r="G41">
-        <v>-2.435069611533716</v>
+        <v>-5.133935583150384</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.041282163219845</v>
       </c>
       <c r="E42">
-        <v>-28.23110679909362</v>
+        <v>-29.74109249339624</v>
       </c>
       <c r="F42">
-        <v>0.3878795756437495</v>
+        <v>-0.7606509999703622</v>
       </c>
       <c r="G42">
-        <v>-3.273663902086501</v>
+        <v>-5.369401445176586</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.78536623345348</v>
       </c>
       <c r="E43">
-        <v>-26.85520242744711</v>
+        <v>-30.24374178706264</v>
       </c>
       <c r="F43">
-        <v>-0.2756352586920293</v>
+        <v>-0.3131437346907909</v>
       </c>
       <c r="G43">
-        <v>-2.411197267650032</v>
+        <v>-4.92327563884994</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.466400764641164</v>
       </c>
       <c r="E44">
-        <v>-27.09128536288899</v>
+        <v>-28.35381485927947</v>
       </c>
       <c r="F44">
-        <v>-0.09665322743875127</v>
+        <v>0.02187123728860759</v>
       </c>
       <c r="G44">
-        <v>-2.365250206110487</v>
+        <v>-4.534726840542299</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.073341099748</v>
       </c>
       <c r="E45">
-        <v>-25.99803022490523</v>
+        <v>-27.29654297576065</v>
       </c>
       <c r="F45">
-        <v>0.2176981196778135</v>
+        <v>-0.0587247691667703</v>
       </c>
       <c r="G45">
-        <v>-2.512665488428694</v>
+        <v>-5.169315383328575</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.609211458510242</v>
       </c>
       <c r="E46">
-        <v>-25.31937499621971</v>
+        <v>-28.46160159761004</v>
       </c>
       <c r="F46">
-        <v>0.9278169040950925</v>
+        <v>0.3379729247272877</v>
       </c>
       <c r="G46">
-        <v>-3.740192600571675</v>
+        <v>-5.157198786654843</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.0790408968948</v>
       </c>
       <c r="E47">
-        <v>-26.04226435901215</v>
+        <v>-26.75229738409681</v>
       </c>
       <c r="F47">
-        <v>0.319424950211204</v>
+        <v>0.1575379370494994</v>
       </c>
       <c r="G47">
-        <v>-3.850284792480138</v>
+        <v>-5.577704281053069</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.48231727516571</v>
       </c>
       <c r="E48">
-        <v>-22.88488548359216</v>
+        <v>-26.52686089104696</v>
       </c>
       <c r="F48">
-        <v>0.4884268109955535</v>
+        <v>-0.197961732433728</v>
       </c>
       <c r="G48">
-        <v>-3.702866199616392</v>
+        <v>-5.008422870119995</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.831686963303511</v>
       </c>
       <c r="E49">
-        <v>-23.24304249285881</v>
+        <v>-26.0382793018854</v>
       </c>
       <c r="F49">
-        <v>0.1488988934057034</v>
+        <v>0.3162531314258847</v>
       </c>
       <c r="G49">
-        <v>-3.8321992821991</v>
+        <v>-4.908146445735471</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.135391109529877</v>
       </c>
       <c r="E50">
-        <v>-21.84724000642259</v>
+        <v>-24.17814520459869</v>
       </c>
       <c r="F50">
-        <v>0.4536883955917535</v>
+        <v>-0.1864714481894961</v>
       </c>
       <c r="G50">
-        <v>-3.27225692023231</v>
+        <v>-4.643905321881924</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.397176547595842</v>
       </c>
       <c r="E51">
-        <v>-22.31360037362851</v>
+        <v>-23.89242113708473</v>
       </c>
       <c r="F51">
-        <v>0.416960241686429</v>
+        <v>0.2568658155843825</v>
       </c>
       <c r="G51">
-        <v>-4.72773164548181</v>
+        <v>-4.843143884071881</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.63166292286989</v>
       </c>
       <c r="E52">
-        <v>-21.35719572015655</v>
+        <v>-24.32965888794732</v>
       </c>
       <c r="F52">
-        <v>0.2360274051995582</v>
+        <v>0.2992641443618697</v>
       </c>
       <c r="G52">
-        <v>-4.779180833707623</v>
+        <v>-4.190939928471144</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.84384698105202</v>
       </c>
       <c r="E53">
-        <v>-22.45233017485349</v>
+        <v>-22.20113572164802</v>
       </c>
       <c r="F53">
-        <v>0.3049550284191023</v>
+        <v>0.06903930557141424</v>
       </c>
       <c r="G53">
-        <v>-3.251066118235435</v>
+        <v>-4.940308395649491</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.037866883361138</v>
       </c>
       <c r="E54">
-        <v>-21.17817608568533</v>
+        <v>-22.7255013124182</v>
       </c>
       <c r="F54">
-        <v>1.194831195978679</v>
+        <v>0.06143986301813158</v>
       </c>
       <c r="G54">
-        <v>-4.739149717046756</v>
+        <v>-6.512291150062561</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.223932544900913</v>
       </c>
       <c r="E55">
-        <v>-20.10607344979139</v>
+        <v>-22.18109722416408</v>
       </c>
       <c r="F55">
-        <v>0.3024964339675933</v>
+        <v>0.1024804976224303</v>
       </c>
       <c r="G55">
-        <v>-4.850052992612341</v>
+        <v>-5.443236542338951</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.398106896373594</v>
       </c>
       <c r="E56">
-        <v>-19.49315807827523</v>
+        <v>-22.98746900528792</v>
       </c>
       <c r="F56">
-        <v>0.8095542034670183</v>
+        <v>0.2943279030085874</v>
       </c>
       <c r="G56">
-        <v>-4.106130372846094</v>
+        <v>-4.968954546200805</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.560123367015036</v>
       </c>
       <c r="E57">
-        <v>-18.66863164485464</v>
+        <v>-21.27337366627457</v>
       </c>
       <c r="F57">
-        <v>0.7200838970254493</v>
+        <v>0.2505909325081763</v>
       </c>
       <c r="G57">
-        <v>-4.762879707472251</v>
+        <v>-5.468505936440208</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.711868691734091</v>
       </c>
       <c r="E58">
-        <v>-20.11253105372633</v>
+        <v>-20.62453391045556</v>
       </c>
       <c r="F58">
-        <v>1.0945871430963</v>
+        <v>0.2988648712737203</v>
       </c>
       <c r="G58">
-        <v>-4.696503269409864</v>
+        <v>-6.718306398971406</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.841517035512885</v>
       </c>
       <c r="E59">
-        <v>-18.25522725269441</v>
+        <v>-20.95701900057273</v>
       </c>
       <c r="F59">
-        <v>0.5492745385681912</v>
+        <v>0.1075509344949661</v>
       </c>
       <c r="G59">
-        <v>-5.582534366994865</v>
+        <v>-5.632344835178739</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.947239050248987</v>
       </c>
       <c r="E60">
-        <v>-16.92743338890539</v>
+        <v>-20.7723297166439</v>
       </c>
       <c r="F60">
-        <v>1.478089772631165</v>
+        <v>0.2133284816280461</v>
       </c>
       <c r="G60">
-        <v>-4.597786111974337</v>
+        <v>-6.242074491510628</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.024391561028667</v>
       </c>
       <c r="E61">
-        <v>-18.64373409476047</v>
+        <v>-19.31771140979606</v>
       </c>
       <c r="F61">
-        <v>1.25902635622603</v>
+        <v>0.160543253986856</v>
       </c>
       <c r="G61">
-        <v>-5.293086749405307</v>
+        <v>-6.094788320468453</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.055913433771218</v>
       </c>
       <c r="E62">
-        <v>-18.18576951836477</v>
+        <v>-19.42474189296735</v>
       </c>
       <c r="F62">
-        <v>0.8387790054377848</v>
+        <v>0.6171170004900679</v>
       </c>
       <c r="G62">
-        <v>-5.428127212497718</v>
+        <v>-7.130475939701748</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.039695024315053</v>
       </c>
       <c r="E63">
-        <v>-16.08690332834169</v>
+        <v>-19.82760399763772</v>
       </c>
       <c r="F63">
-        <v>0.3450024505074443</v>
+        <v>0.5809049194766875</v>
       </c>
       <c r="G63">
-        <v>-6.389651990560259</v>
+        <v>-7.349538048580862</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.967142322193681</v>
       </c>
       <c r="E64">
-        <v>-17.17457032939999</v>
+        <v>-19.53233843538959</v>
       </c>
       <c r="F64">
-        <v>0.3453950966563713</v>
+        <v>-0.03334773378200745</v>
       </c>
       <c r="G64">
-        <v>-5.041948764796195</v>
+        <v>-7.099982504739521</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.822943650803797</v>
       </c>
       <c r="E65">
-        <v>-15.94112269308677</v>
+        <v>-19.14979106511763</v>
       </c>
       <c r="F65">
-        <v>0.9043558825130049</v>
+        <v>-0.2504777406690082</v>
       </c>
       <c r="G65">
-        <v>-4.910904130169684</v>
+        <v>-7.035824132188445</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.608137510130076</v>
       </c>
       <c r="E66">
-        <v>-17.22712779873302</v>
+        <v>-19.01712036211492</v>
       </c>
       <c r="F66">
-        <v>0.5317694786122321</v>
+        <v>-0.253213838200455</v>
       </c>
       <c r="G66">
-        <v>-5.984808687108325</v>
+        <v>-6.728860418150603</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.315201860100355</v>
       </c>
       <c r="E67">
-        <v>-15.34020777769094</v>
+        <v>-18.04478000860996</v>
       </c>
       <c r="F67">
-        <v>0.4887888075505769</v>
+        <v>-0.03183182143488435</v>
       </c>
       <c r="G67">
-        <v>-5.328436754673644</v>
+        <v>-7.380408885734565</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.936784320231525</v>
       </c>
       <c r="E68">
-        <v>-14.68222503285044</v>
+        <v>-18.28445402393992</v>
       </c>
       <c r="F68">
-        <v>0.813422679238092</v>
+        <v>-0.08915484570861014</v>
       </c>
       <c r="G68">
-        <v>-5.575459731177443</v>
+        <v>-6.71629358728353</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.477581252056174</v>
       </c>
       <c r="E69">
-        <v>-15.85011395095462</v>
+        <v>-18.02978623117056</v>
       </c>
       <c r="F69">
-        <v>0.8193769841294148</v>
+        <v>-0.1205963588492682</v>
       </c>
       <c r="G69">
-        <v>-5.412650412101625</v>
+        <v>-7.630563638318514</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.933690406602252</v>
       </c>
       <c r="E70">
-        <v>-16.16717505860166</v>
+        <v>-17.86135869740328</v>
       </c>
       <c r="F70">
-        <v>0.4055304282626014</v>
+        <v>-0.3560341137055409</v>
       </c>
       <c r="G70">
-        <v>-5.750845812756952</v>
+        <v>-7.716005508141564</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.307636250910392</v>
       </c>
       <c r="E71">
-        <v>-13.5059720232541</v>
+        <v>-17.52830754803515</v>
       </c>
       <c r="F71">
-        <v>0.3064883364816841</v>
+        <v>-0.7475147496967676</v>
       </c>
       <c r="G71">
-        <v>-5.155917605531145</v>
+        <v>-6.965292959474272</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.60823898417555</v>
       </c>
       <c r="E72">
-        <v>-15.3076525780498</v>
+        <v>-18.16500193656559</v>
       </c>
       <c r="F72">
-        <v>-0.09372743377206341</v>
+        <v>-0.1898039702509585</v>
       </c>
       <c r="G72">
-        <v>-4.263136305591569</v>
+        <v>-6.852803932595377</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.838605581932074</v>
       </c>
       <c r="E73">
-        <v>-14.48885466424891</v>
+        <v>-18.0687718639026</v>
       </c>
       <c r="F73">
-        <v>0.4817443711571699</v>
+        <v>-0.3110164872004018</v>
       </c>
       <c r="G73">
-        <v>-5.060163386353265</v>
+        <v>-7.137375116605589</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.012704354855574</v>
       </c>
       <c r="E74">
-        <v>-16.71565477346268</v>
+        <v>-17.7160173241271</v>
       </c>
       <c r="F74">
-        <v>0.09177799077826067</v>
+        <v>-0.7070514871722202</v>
       </c>
       <c r="G74">
-        <v>-5.382848881157106</v>
+        <v>-6.232245481804532</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.144626708688857</v>
       </c>
       <c r="E75">
-        <v>-17.17455674397797</v>
+        <v>-18.25578425499736</v>
       </c>
       <c r="F75">
-        <v>-0.4661257982724007</v>
+        <v>-0.2696204829803021</v>
       </c>
       <c r="G75">
-        <v>-4.206840478696263</v>
+        <v>-5.989138880673692</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.244231802275157</v>
       </c>
       <c r="E76">
-        <v>-14.7036311294847</v>
+        <v>-17.85596075638614</v>
       </c>
       <c r="F76">
-        <v>-0.1344450050892703</v>
+        <v>-0.9574271914031763</v>
       </c>
       <c r="G76">
-        <v>-5.272663993973543</v>
+        <v>-5.745277475159898</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.332560630919289</v>
       </c>
       <c r="E77">
-        <v>-16.10425644073909</v>
+        <v>-17.39868903651361</v>
       </c>
       <c r="F77">
-        <v>-0.7913817738794182</v>
+        <v>-1.085423209014145</v>
       </c>
       <c r="G77">
-        <v>-3.363416102201682</v>
+        <v>-6.138298820491094</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.4251415890890248</v>
       </c>
       <c r="E78">
-        <v>-15.15578114525455</v>
+        <v>-18.67788784572632</v>
       </c>
       <c r="F78">
-        <v>-0.7176115148231083</v>
+        <v>-1.638543176313639</v>
       </c>
       <c r="G78">
-        <v>-5.446249138779688</v>
+        <v>-6.11370146713431</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.4653804080928612</v>
       </c>
       <c r="E79">
-        <v>-17.08982899529446</v>
+        <v>-17.63244433631554</v>
       </c>
       <c r="F79">
-        <v>-0.4086611231727962</v>
+        <v>-1.129929732831757</v>
       </c>
       <c r="G79">
-        <v>-3.003973620275313</v>
+        <v>-5.33781884073194</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.317951831613378</v>
       </c>
       <c r="E80">
-        <v>-16.588323141315</v>
+        <v>-19.29036395526374</v>
       </c>
       <c r="F80">
-        <v>-0.823956493627106</v>
+        <v>-1.292254123982139</v>
       </c>
       <c r="G80">
-        <v>-3.233864523613383</v>
+        <v>-5.379329771248861</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>2.122168800070122</v>
       </c>
       <c r="E81">
-        <v>-16.01687953476109</v>
+        <v>-20.67293876912355</v>
       </c>
       <c r="F81">
-        <v>-0.6437484786176848</v>
+        <v>-1.006681917173635</v>
       </c>
       <c r="G81">
-        <v>-3.493725795718474</v>
+        <v>-4.69297753841054</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>2.869398274127986</v>
       </c>
       <c r="E82">
-        <v>-17.39791466745829</v>
+        <v>-20.70218365426508</v>
       </c>
       <c r="F82">
-        <v>-0.9381635074510738</v>
+        <v>-1.173137376561779</v>
       </c>
       <c r="G82">
-        <v>-3.424628089222806</v>
+        <v>-4.4302460233229</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>3.546560362379317</v>
       </c>
       <c r="E83">
-        <v>-19.01426742349008</v>
+        <v>-22.23030815120543</v>
       </c>
       <c r="F83">
-        <v>-1.712416152927896</v>
+        <v>-1.680442827914641</v>
       </c>
       <c r="G83">
-        <v>-2.536117393028891</v>
+        <v>-4.470806827270051</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>4.150971847363778</v>
       </c>
       <c r="E84">
-        <v>-19.6598059217575</v>
+        <v>-21.87692868201688</v>
       </c>
       <c r="F84">
-        <v>-0.9889871610824347</v>
+        <v>-2.015645010927072</v>
       </c>
       <c r="G84">
-        <v>-3.083191664484533</v>
+        <v>-4.754265667979068</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>4.678150565487156</v>
       </c>
       <c r="E85">
-        <v>-21.10297624631395</v>
+        <v>-22.21474378604107</v>
       </c>
       <c r="F85">
-        <v>-1.241915893648819</v>
+        <v>-1.667835904411435</v>
       </c>
       <c r="G85">
-        <v>-2.367845673813275</v>
+        <v>-4.680612650821362</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>5.121779135293369</v>
       </c>
       <c r="E86">
-        <v>-21.84489878536062</v>
+        <v>-23.74106595032636</v>
       </c>
       <c r="F86">
-        <v>-1.554381048189209</v>
+        <v>-1.758800585647655</v>
       </c>
       <c r="G86">
-        <v>-4.014226318130387</v>
+        <v>-4.715174746251353</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>5.481435970766095</v>
       </c>
       <c r="E87">
-        <v>-22.29071799446776</v>
+        <v>-24.44315603200157</v>
       </c>
       <c r="F87">
-        <v>-2.222605979577306</v>
+        <v>-1.574827640792509</v>
       </c>
       <c r="G87">
-        <v>-2.600606820133894</v>
+        <v>-3.486952419545125</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>5.752886797782323</v>
       </c>
       <c r="E88">
-        <v>-22.28062855437867</v>
+        <v>-24.93707669201817</v>
       </c>
       <c r="F88">
-        <v>-2.071958255336785</v>
+        <v>-2.214740631087725</v>
       </c>
       <c r="G88">
-        <v>-2.025737208330531</v>
+        <v>-4.784351905839964</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>5.933822712943337</v>
       </c>
       <c r="E89">
-        <v>-24.16344124949579</v>
+        <v>-26.84728212640769</v>
       </c>
       <c r="F89">
-        <v>-2.390299019865232</v>
+        <v>-2.440773930820014</v>
       </c>
       <c r="G89">
-        <v>-2.758317899079234</v>
+        <v>-4.321087405256511</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>6.023643873194705</v>
       </c>
       <c r="E90">
-        <v>-26.03200736538477</v>
+        <v>-26.85969014518871</v>
       </c>
       <c r="F90">
-        <v>-2.734817022689547</v>
+        <v>-2.634843845947883</v>
       </c>
       <c r="G90">
-        <v>-3.429325753343032</v>
+        <v>-4.625723805780246</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>6.018120344343704</v>
       </c>
       <c r="E91">
-        <v>-29.32817491219184</v>
+        <v>-28.06476689184387</v>
       </c>
       <c r="F91">
-        <v>-2.634945735138427</v>
+        <v>-2.807994170685452</v>
       </c>
       <c r="G91">
-        <v>-3.038164934604906</v>
+        <v>-5.057379217554738</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>5.917780778930854</v>
       </c>
       <c r="E92">
-        <v>-29.91004759438542</v>
+        <v>-30.54077345417375</v>
       </c>
       <c r="F92">
-        <v>-2.976914851464327</v>
+        <v>-2.458178758320235</v>
       </c>
       <c r="G92">
-        <v>-3.509093348111771</v>
+        <v>-4.671184217125518</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>5.721078992009684</v>
       </c>
       <c r="E93">
-        <v>-32.28894103162081</v>
+        <v>-32.15896929912666</v>
       </c>
       <c r="F93">
-        <v>-2.723476672945222</v>
+        <v>-2.616442492462095</v>
       </c>
       <c r="G93">
-        <v>-3.318028522858274</v>
+        <v>-5.513727988506653</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>5.426628102564094</v>
       </c>
       <c r="E94">
-        <v>-34.22625391142024</v>
+        <v>-34.47879332140599</v>
       </c>
       <c r="F94">
-        <v>-2.771907173149895</v>
+        <v>-2.674175558600206</v>
       </c>
       <c r="G94">
-        <v>-3.565720229561005</v>
+        <v>-4.943453413911798</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>5.04123910324727</v>
       </c>
       <c r="E95">
-        <v>-34.40266514486304</v>
+        <v>-35.98696083339453</v>
       </c>
       <c r="F95">
-        <v>-2.189186325078763</v>
+        <v>-3.289506746217346</v>
       </c>
       <c r="G95">
-        <v>-3.666665384144462</v>
+        <v>-4.900734134273043</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>4.563831182239684</v>
       </c>
       <c r="E96">
-        <v>-37.54447286240766</v>
+        <v>-37.2456456553525</v>
       </c>
       <c r="F96">
-        <v>-3.119549777817569</v>
+        <v>-3.200829187380256</v>
       </c>
       <c r="G96">
-        <v>-3.623048946664564</v>
+        <v>-5.486598067812325</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>4.010179749400603</v>
       </c>
       <c r="E97">
-        <v>-38.41368174886193</v>
+        <v>-39.49462396601884</v>
       </c>
       <c r="F97">
-        <v>-4.079607716844529</v>
+        <v>-3.325650901103697</v>
       </c>
       <c r="G97">
-        <v>-4.549289930369553</v>
+        <v>-5.807221092745201</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>3.383204772807869</v>
       </c>
       <c r="E98">
-        <v>-41.05844868779865</v>
+        <v>-41.62770730564387</v>
       </c>
       <c r="F98">
-        <v>-3.300673967174486</v>
+        <v>-3.838966157963869</v>
       </c>
       <c r="G98">
-        <v>-4.155507159564324</v>
+        <v>-6.632298425861141</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>2.718927443513227</v>
       </c>
       <c r="E99">
-        <v>-42.10283706276564</v>
+        <v>-44.84171022005577</v>
       </c>
       <c r="F99">
-        <v>-4.099774321265683</v>
+        <v>-3.812118770439137</v>
       </c>
       <c r="G99">
-        <v>-5.357099457952654</v>
+        <v>-6.552593731457648</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>2.007294345703407</v>
       </c>
       <c r="E100">
-        <v>-45.99933308758455</v>
+        <v>-46.11942368979396</v>
       </c>
       <c r="F100">
-        <v>-3.684695154703503</v>
+        <v>-4.222610438324613</v>
       </c>
       <c r="G100">
-        <v>-5.23551967302292</v>
+        <v>-6.567474633656672</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.328283892975385</v>
       </c>
       <c r="E101">
-        <v>-46.92257572589835</v>
+        <v>-47.75569041027448</v>
       </c>
       <c r="F101">
-        <v>-4.03577382735799</v>
+        <v>-3.851318772674416</v>
       </c>
       <c r="G101">
-        <v>-4.499032538537877</v>
+        <v>-6.27899700591012</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>0.6181586804418723</v>
       </c>
       <c r="E102">
-        <v>-49.03763460685435</v>
+        <v>-50.3168515299631</v>
       </c>
       <c r="F102">
-        <v>-3.736574148406031</v>
+        <v>-4.116808868536851</v>
       </c>
       <c r="G102">
-        <v>-5.876980908348723</v>
+        <v>-6.395164048883146</v>
       </c>
     </row>
   </sheetData>
